--- a/public/policy_templates/drgadget.xlsx
+++ b/public/policy_templates/drgadget.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\project\friendsure\admin-portal\public\policy_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A03ECE5-C65D-4652-8B8D-5106FE67007D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2C1E7875-616D-48A2-B2F0-33F6624D2020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{07A3B718-5E1F-4F69-8AFD-C383E5237541}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>no</t>
   </si>
@@ -54,9 +54,6 @@
     <t>Ahmad</t>
   </si>
   <si>
-    <t>ahmadtest@yopmail.com</t>
-  </si>
-  <si>
     <t>NOKIA</t>
   </si>
   <si>
@@ -85,6 +82,15 @@
   </si>
   <si>
     <t>+628327163124</t>
+  </si>
+  <si>
+    <t>01/01/2024</t>
+  </si>
+  <si>
+    <t>01/01/2030</t>
+  </si>
+  <si>
+    <t>ahmadtest@example.com</t>
   </si>
 </sst>
 </file>
@@ -129,10 +135,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -453,14 +458,14 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="11.36328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.08984375" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18.08984375" style="2" customWidth="1"/>
     <col min="5" max="5" width="22.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.81640625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.81640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.90625" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
@@ -468,34 +473,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
         <v>3</v>
       </c>
       <c r="F1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" t="s">
         <v>13</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>14</v>
       </c>
-      <c r="H1" t="s">
-        <v>15</v>
-      </c>
       <c r="I1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="K1" t="s">
-        <v>12</v>
       </c>
       <c r="L1" t="s">
         <v>4</v>
@@ -511,17 +516,17 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>16</v>
+      <c r="D2" s="2" t="s">
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
         <v>6</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>7</v>
-      </c>
-      <c r="G2" t="s">
-        <v>8</v>
       </c>
       <c r="H2">
         <v>10299920</v>
@@ -529,11 +534,11 @@
       <c r="I2">
         <v>12345</v>
       </c>
-      <c r="J2" s="2">
-        <v>45292</v>
-      </c>
-      <c r="K2" s="2">
-        <v>47484</v>
+      <c r="J2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>17</v>
       </c>
       <c r="L2">
         <v>100000</v>
